--- a/artfynd/A 45325-2025 artfynd.xlsx
+++ b/artfynd/A 45325-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>35747</v>
+        <v>35748</v>
       </c>
       <c r="B2" t="n">
-        <v>57584</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>larv</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>362542.9967342656</v>
+        <v>362543</v>
       </c>
       <c r="R2" t="n">
-        <v>6228841.214360318</v>
+        <v>6228841</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,27 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1985-07-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1980-10-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1985-07-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1980-10-04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Håvning gav flera larver</t>
+          <t>under en sten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>35745</v>
+        <v>88165808</v>
       </c>
       <c r="B3" t="n">
-        <v>57576</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,44 +797,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rögle-Välinge 1, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>362542.9967342656</v>
+        <v>362543</v>
       </c>
       <c r="R3" t="n">
-        <v>6228841.214360318</v>
+        <v>6228841</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,27 +859,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1981-04-04</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1981-04-04</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>stora mängder</t>
+          <t>talrik</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,15 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>35746</v>
+        <v>88165805</v>
       </c>
       <c r="B4" t="n">
-        <v>57574</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,44 +917,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rögle-Välinge 1, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>362542.9967342656</v>
+        <v>362543</v>
       </c>
       <c r="R4" t="n">
-        <v>6228841.214360318</v>
+        <v>6228841</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1004,27 +979,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1981-04-04</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1981-04-04</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fåtalig</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,15 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35748</v>
+        <v>35747</v>
       </c>
       <c r="B5" t="n">
-        <v>57586</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,31 +1032,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>larv</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1100,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>362542.9967342656</v>
+        <v>362543</v>
       </c>
       <c r="R5" t="n">
-        <v>6228841.214360318</v>
+        <v>6228841</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1130,27 +1091,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1980-10-04</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1985-07-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1980-10-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1985-07-28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>under en sten</t>
+          <t>Håvning gav flera larver</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,47 +1128,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88165790</v>
+        <v>35745</v>
       </c>
       <c r="B6" t="n">
-        <v>27380</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101779</v>
+        <v>208249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordlig buksimmare</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sigara fallenoidea</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hungerford, 1926)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>vattenhåvning</t>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1226,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>362542.9967342656</v>
+        <v>362543</v>
       </c>
       <c r="R6" t="n">
-        <v>6228841.214360318</v>
+        <v>6228841</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1256,22 +1203,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>1981-04-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>1981-04-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>stora mängder</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1222,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1296,6 +1237,118 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>35746</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rögle-Välinge 1, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>362543</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6228841</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Helsingborg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Välinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1981-04-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1981-04-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fåtalig</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Göran Paulson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Göran Paulson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
